--- a/excel/output_stats_sfvv/floyd-warshall/PerSubgraphStats.xlsx
+++ b/excel/output_stats_sfvv/floyd-warshall/PerSubgraphStats.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1199,10 +1199,10 @@
         <v>0.6</v>
       </c>
       <c r="N16" t="n">
-        <v>350.15</v>
+        <v>332.47</v>
       </c>
       <c r="O16" t="n">
-        <v>350.17</v>
+        <v>345.38</v>
       </c>
     </row>
     <row r="17">
@@ -1210,34 +1210,34 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>1.94691e-09</v>
+        <v>9.33517</v>
       </c>
       <c r="D17" t="n">
-        <v>7.666670000000001e-09</v>
+        <v>17.7206</v>
       </c>
       <c r="E17" t="n">
-        <v>0.253945</v>
+        <v>0.526797</v>
       </c>
       <c r="F17" t="n">
-        <v>1.49263e-17</v>
+        <v>165.425</v>
       </c>
       <c r="G17" t="n">
-        <v>913044000</v>
+        <v>1462030000</v>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>25908100000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>10922100000</v>
       </c>
       <c r="K17" t="n">
-        <v>23</v>
+        <v>53161800000</v>
       </c>
       <c r="L17" t="n">
         <v>3000000000</v>
@@ -1246,10 +1246,10 @@
         <v>0.6</v>
       </c>
       <c r="N17" t="n">
-        <v>350.151</v>
+        <v>332.47</v>
       </c>
       <c r="O17" t="n">
-        <v>350.19</v>
+        <v>360.62</v>
       </c>
     </row>
     <row r="18">
@@ -1257,34 +1257,34 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>2.74083e-09</v>
+        <v>1.94691e-09</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1e-08</v>
+        <v>7.666670000000001e-09</v>
       </c>
       <c r="E18" t="n">
-        <v>0.249166</v>
+        <v>0.253945</v>
       </c>
       <c r="F18" t="n">
-        <v>3.01491e-17</v>
+        <v>1.49263e-17</v>
       </c>
       <c r="G18" t="n">
-        <v>818182000</v>
+        <v>913044000</v>
       </c>
       <c r="H18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="L18" t="n">
         <v>3000000000</v>
@@ -1293,10 +1293,10 @@
         <v>0.6</v>
       </c>
       <c r="N18" t="n">
-        <v>350.15</v>
+        <v>350.151</v>
       </c>
       <c r="O18" t="n">
-        <v>350.17</v>
+        <v>350.19</v>
       </c>
     </row>
     <row r="19">
@@ -1304,34 +1304,34 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>4.76522e-10</v>
+        <v>2.74083e-09</v>
       </c>
       <c r="D19" t="n">
-        <v>2e-09</v>
+        <v>1.1e-08</v>
       </c>
       <c r="E19" t="n">
-        <v>0.238261</v>
+        <v>0.249166</v>
       </c>
       <c r="F19" t="n">
-        <v>9.530439999999999e-19</v>
+        <v>3.01491e-17</v>
       </c>
       <c r="G19" t="n">
-        <v>500000000</v>
+        <v>818182000</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="L19" t="n">
         <v>3000000000</v>
@@ -1351,7 +1351,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20" t="n">
         <v>4.76522e-10</v>
@@ -1398,34 +1398,34 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>6.24265e-10</v>
+        <v>4.76522e-10</v>
       </c>
       <c r="D21" t="n">
-        <v>2.33333e-09</v>
+        <v>2e-09</v>
       </c>
       <c r="E21" t="n">
-        <v>0.267542</v>
+        <v>0.238261</v>
       </c>
       <c r="F21" t="n">
-        <v>1.45662e-18</v>
+        <v>9.530439999999999e-19</v>
       </c>
       <c r="G21" t="n">
-        <v>857143000</v>
+        <v>500000000</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
         <v>3000000000</v>
@@ -1434,7 +1434,7 @@
         <v>0.6</v>
       </c>
       <c r="N21" t="n">
-        <v>350.151</v>
+        <v>350.15</v>
       </c>
       <c r="O21" t="n">
         <v>350.17</v>
@@ -1445,7 +1445,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C22" t="n">
         <v>6.24265e-10</v>
@@ -1492,34 +1492,34 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C23" t="n">
-        <v>1.48585e-09</v>
+        <v>6.24265e-10</v>
       </c>
       <c r="D23" t="n">
-        <v>5.66667e-09</v>
+        <v>2.33333e-09</v>
       </c>
       <c r="E23" t="n">
-        <v>0.262208</v>
+        <v>0.267542</v>
       </c>
       <c r="F23" t="n">
-        <v>8.419790000000001e-18</v>
+        <v>1.45662e-18</v>
       </c>
       <c r="G23" t="n">
-        <v>705882000</v>
+        <v>857143000</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="L23" t="n">
         <v>3000000000</v>
@@ -1528,7 +1528,7 @@
         <v>0.6</v>
       </c>
       <c r="N23" t="n">
-        <v>350.15</v>
+        <v>350.151</v>
       </c>
       <c r="O23" t="n">
         <v>350.17</v>
@@ -1539,45 +1539,92 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.48585e-09</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5.66667e-09</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.262208</v>
+      </c>
+      <c r="F24" t="n">
+        <v>8.419790000000001e-18</v>
+      </c>
+      <c r="G24" t="n">
+        <v>705882000</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>17</v>
+      </c>
+      <c r="L24" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N24" t="n">
+        <v>350.15</v>
+      </c>
+      <c r="O24" t="n">
+        <v>350.17</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="C24" t="n">
+      <c r="B25" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" t="n">
         <v>1.21265e-10</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D25" t="n">
         <v>3.33333e-10</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E25" t="n">
         <v>0.363794</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F25" t="n">
         <v>4.04216e-20</v>
       </c>
-      <c r="G24" t="n">
-        <v>3000000000</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="G25" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="H25" t="n">
         <v>1</v>
       </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>3000000000</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N24" t="n">
+      <c r="L25" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N25" t="n">
         <v>350.151</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O25" t="n">
         <v>350.22</v>
       </c>
     </row>
